--- a/tenders_grants.xlsx
+++ b/tenders_grants.xlsx
@@ -426,15 +426,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,7 +448,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Detail Page URL</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -455,403 +458,268 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Geographic Area</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Focus Sector</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Focus Sector</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Geographic Area</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source Link</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Amount (USD)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Employment-Intensive Investment Programme (EIIP) Workshop in Duhok, Iraq</t>
+          <t>Strengthening civil society &amp; youth for climate action in Egypt – Baseline study</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/employment-intensive-investment-programme-eiip-workshop-in-duhok-iraq/</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>CARE Egypt Foundation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Economic Growth, Events management</t>
+          <t>Climate Change and Global Warming, Democratic Governance, Youth Empowerment, Monitoring and evaluation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Iraq</t>
-        </is>
-      </c>
+          <t>30 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/strengthening-civil-society-youth-for-climate-action-in-egypt-baseline-study/</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Seminar package, event management services Tunisia Office – JPRWEE Project 2026</t>
+          <t>Hiring A Social Media Agency</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/seminar-package-event-management-services-tunisia-office-jprwee-project-2026/</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UN Women</t>
+          <t>Sawiris Foundation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Women Rights and Empowerment, Events management</t>
+          <t>Economic Growth, Entrepreneurship, Women Rights and Empowerment, Youth Empowerment, Media and communication</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
+          <t>26 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/hiring-a-social-media-agency/</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consultancy Services for the Development, Design, and Documentation of Communications and Advocacy Tools for Just Transition in Jordan</t>
+          <t>Project to Strengthen Analytical Capabilities for System Stabilization in Lebanon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/consultancy-services-for-the-development-design-and-documentation-of-communications-and-advocacy-tools-for-just-transition-in-jordan-2/</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>JICA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Economic Growth, Environment and Energy, Advocacy and awareness raising, Media and communication</t>
+          <t>Environment and Energy, Capacity building and training, Institutional Strengthening, Research and assessment</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordan</t>
-        </is>
-      </c>
+          <t>03 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/project-to-strengthen-analytical-capabilities-for-system-stabilization-in-lebanon/</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Single Source Justification : Attorney service – Kuwait Buffer Zone Land Rights Registration</t>
+          <t>Guide orientation, canevas suivi-évaluation, formation Centres de jours pour personnes âgées</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/single-source-justification-attorney-service-kuwait-buffer-zone-land-rights-registration/</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>United States Embassy</t>
+          <t>UN Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Democratic Governance, Legal Services</t>
+          <t>Social Development, Women Rights and Empowerment, Capacity building and training, Institutional Strengthening</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
+          <t>25 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/guide-orientation-canevas-suivi-evaluation-formation-centres-de-jours-pour-personnes-agees/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Development of a Climate-Related Disaster Risk Reduction Plan for Damietta, Egypt</t>
+          <t>Apply for ClimateLaunchpad 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/development-of-a-climate-related-disaster-risk-reduction-plan-for-damietta-egypt/</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>ClimateLaunchpad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>Egypt, Morocco, Turkey</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Climate Change and Global Warming, Environment and Energy, Environmental Services, Institutional Strengthening</t>
+          <t>Climate Change and Global Warming, Entrepreneurship, Capacity building and training, Environmental Services</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Egypt</t>
-        </is>
-      </c>
+          <t>15 May 2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/apply-for-climatelaunchpad-2026/</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiple workshops and Trainings for the WHO that will be held in Amman &amp; Irbid, Jordan from 14 April 2026 to 30 July 2026</t>
+          <t>The 2026-2027 ECD in Crisis Research Fellowship Program</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/multiple-workshops-and-trainings-for-the-who-that-will-be-held-in-amman-irbid-jordan-from-14-april-2026-to-30-july-2026/</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHO</t>
+          <t>Moving Minds Alliance</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>MENA region</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Health, Events management</t>
+          <t>Child Rights, Research and assessment</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>THAMM+ International Consultancy Firm to conduct an Operational Review</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://darpe.me/darpe-entries/thamm-international-consultancy-firm-to-conduct-an-operational-review/</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>24 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Social Development, Research and assessment</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Egypt, Morocco, Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Call for External Collaborator _ Development of a Just Transition Finance Strategy Outline for Jordan</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://darpe.me/darpe-entries/call-for-external-collaborator-_-development-of-a-just-transition-finance-strategy-outline-for-jordan/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>23 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Economic Growth, Financial Management Services</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Call for External Collaborator_Support to GFJTU in Developing a Workers’ Position Paper on Just Transition and NDC 3.0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://darpe.me/darpe-entries/call-for-external-collaborator_support-to-gfjtu-in-developing-a-workers-position-paper-on-just-transition-and-ndc-3-0/</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>23 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Economic Growth, Research and assessment</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Call for External Collaborator_Support to the Jordan Chamber of Industry (JCI) in Developing an Employers’ Position Paper on Just Transition and NDC 3.0</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://darpe.me/darpe-entries/call-for-external-collaborator_support-to-the-jordan-chamber-of-industry-jci-in-developing-an-employers-position-paper-on-just-transition-and-ndc-3-0/</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>23 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Economic Growth, Research and assessment</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Call for External Collaborator_Technical Support for Developing a Resource Efficiency / Waste Management Partnership</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://darpe.me/darpe-entries/call-for-external-collaborator_technical-support-for-developing-a-resource-efficiency-waste-management-partnership/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>23 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Waste Management, Business Development, Feasibility studies</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sector-Wide Cybersecurity, Business Continuity, Framework &amp; Policy Development</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://darpe.me/darpe-entries/sector-wide-cybersecurity-business-continuity-framework-policy-development-2/</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>World Bank</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>30 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Information Communication and Technology, Institutional Strengthening</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Palestine</t>
-        </is>
-      </c>
+          <t>31 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/the-2026-2027-ecd-in-crisis-research-fellowship-program/</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tenders_grants.xlsx
+++ b/tenders_grants.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -436,8 +436,10 @@
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,10 +480,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Original Link</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Attachments</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Amount (USD)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
@@ -523,8 +535,18 @@
           <t>https://darpe.me/darpe-entries/strengthening-civil-society-youth-for-climate-action-in-egypt-baseline-study/</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://care.org.eg/job/%d8%aa%d9%86%d9%81%d9%8a%d8%b0-%d8%af%d8%b1%d8%a7%d8%b3%d8%a9-%d8%ae%d8%b7-%d8%a7%d9%84%d8%a3%d8%b3%d8%a7%d8%b3/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/BMZ-Basline-Study-TOR-en.docx, https://darpe.me/wp-content/uploads/2026/03/CEF-consultancy-TOR-in-Arabic-4.doc</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,8 +584,18 @@
           <t>https://darpe.me/darpe-entries/hiring-a-social-media-agency/</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://sawirisfoundation.org/consultancies/hiring-a-social-media-agency/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Sawiris-Foundation_Hiring-Social-Media-Agency-1.docx</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -601,8 +633,18 @@
           <t>https://darpe.me/darpe-entries/project-to-strengthen-analytical-capabilities-for-system-stabilization-in-lebanon/</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www2.jica.go.jp/ja/announce/index.php?contract=1&amp;p=1&amp;fbclid=IwAR3-vltmyrwUkBXZ0hZDpVRYlCgfwWyheVk55pUsJGnkE-MVJc77vFkG2TI</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/20260318_255908_1_02.pdf</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -640,8 +682,18 @@
           <t>https://darpe.me/darpe-entries/guide-orientation-canevas-suivi-evaluation-formation-centres-de-jours-pour-personnes-agees/</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.ungm.org/Public/Notice/292732</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/170424091_RFP-Centres-de-jours-PA-VF-03.03.26.docx, https://darpe.me/wp-content/uploads/2026/03/UNW-MAR-2025-00111_SUPPLIER.pdf</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -679,8 +731,18 @@
           <t>https://darpe.me/darpe-entries/apply-for-climatelaunchpad-2026/</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://climatelaunchpad.org/</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://climatelaunchpad.org/application-form/</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -719,7 +781,13 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/2026-27-ECDiC-Research-Fellowship-Programme-Fellows-TOR.pdf</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tenders_grants.xlsx
+++ b/tenders_grants.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="69" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
@@ -789,6 +789,774 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Establishment of Coaching &amp; Technical Experts Pool</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Syrian Association for Relief and Development (SARD)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Syria, Turkey</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Agriculture, Economic Growth, Entrepreneurship, Women Rights and Empowerment, Capacity building and training, Feasibility studies, Financial Management Services, Human Resources Management , Legal Services</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/establishment-of-coaching-technical-experts-pool/</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/CALL-FOR-EXPRESSIONS-OF-INTEREST-EOI.pdf</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Enhancing Economic Opportunities for Women and Youth within the framework of PROJECT PIHOS–Phase 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EBRD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Entrepreneurship, Food Security, Refugees and Migration, Capacity building and training</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>08 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/enhancing-economic-opportunities-for-women-and-youth-within-the-framework-of-project-pihos-phase-2/</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://eu.smart.gep.com/publicrfx/ebrd?oloc=215#/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Event-Summary-Overview-.docx, https://darpe.me/wp-content/uploads/2026/03/French-ToRs-Gender-and-Economic-Inclusion-Technical-Assistance-Framework-FRENCH.docx, https://darpe.me/wp-content/uploads/2026/03/Access-to-Skills-ToR-Phase-2_Gender-and-Economic-Inclusion-Technical-Assistance-Framework-ENGLISH.docx</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Recruitment of Consultancy Firm UN Women Tunisia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>UN Women</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Democratic Governance, Women Rights and Empowerment, Capacity building and training</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>27 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/recruitment-of-consultancy-firm-un-women-tunisia/</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.ungm.org/Public/Notice/294185</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/172079988_Request-for-Quotation-RFQ-PBF-Expert-Consultancy-Company-Training-April-2026_VF2.docx, https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNW-TUN-2026-00009_English.pdf</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>État des lieux et Plan d’action national pour la protection des pollinisateurs en Tunisie</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>UNDP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Agriculture, Environment and Energy, Institutional Strengthening, Research and assessment</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>23 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/etat-des-lieux-et-plan-daction-national-pour-la-protection-des-pollinisateurs-en-tunisie/</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43302</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/170284814_TERMES-DE-REFERENCE_pollinisateurs_-VFF.docx, https://darpe.me/wp-content/uploads/2026/03/UNDP-TUN-00950_SUPPLIER.pdf</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Digitalisation du Manuel de l’Offre de Services de Placement à l’International de l’ANAPEC.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Economic Growth, Entrepreneurship, ICT Solutions</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>05 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/digitalisation-du-manuel-de-loffre-de-services-de-placement-a-linternational-de-lanapec/</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.ungm.org/Public/Notice/294207</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/RFQ_Services_FR-1.pdf, https://darpe.me/wp-content/uploads/2026/03/TDR_Digitalisation_Manuel_Offre_Services_ANAPEC_OIT-VF.pdf</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Provision of Digital Product Passport (DPP) Pilot Implementation Services for Textile SMEs in Egypt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>UNIDO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Entrepreneurship, Industry, ICT Solutions</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>01 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/provision-of-digital-product-passport-dpp-pilot-implementation-services-for-textile-smes-in-egypt/</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.unido.org/get-involved/procurement/procurement-opportunities</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/TOR_TIGARA-DPP.pdf, https://darpe.me/wp-content/uploads/2026/03/RFx-7000008382-instructions-to-bidders.pdf</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Call for expression of interest from Egyptian SMEs: Demonstration of Resource Efficient production in Automotive, Electric and Electronics sectors</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UNIDO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Entrepreneurship, Industry, Waste Management, Business Development, Capacity building and training</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/call-for-expression-of-interest-from-egyptian-smes-demonstration-of-resource-efficient-production-in-automotive-electric-and-electronics-sectors-in-arabic/</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://greenforwardindustry.eu/news/eoi-demonstration-resource-efficient-production-egypt-automotive-sector/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://forms.office.com/Pages/ResponsePage.aspx?id=MUlqQlzsy0-dEDNj69-SgAAXvVZaHG1DrWaMyOV_m8FUQkFRV0U2VkdCRVQ2M1RYOFE4TEhPU05LTS4u</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Call for Consultants-Generic call for trainers</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ABAAD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Democratic Governance, Capacity building and training</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>24 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/call-for-consultants-generic-call-for-trainers/</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://ee-eu.kobotoolbox.org/x/ny5U9FMs</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Generic-call-for-trainers.docx</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Recrutement Formateur/trice en Entrepreneuriat</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Création et Créativité pour le Développement et l`embauche (CCDE)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Economic Growth, Capacity building and training</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>24 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/recrutement-formateur-trice-en-entrepreneuriat/</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Recrutement-Formateur-trice-en-Entrepreneuriat.pdf</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Call for Proposals of the Facility Investing for Employment (IFE)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Invest for Jobs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Egypt, Morocco, Tunisia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Economic Growth, Capacity building and training</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>01 Jun 2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/call-for-proposals-of-the-facility-investing-for-employment-ife/</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://invest-for-jobs.com/en/ife-download-center</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Guidelines-for-Applicants-CfP-2026-Labour-Migration-final-05-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Announcement of the “Polish Development Aid 2026”</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Polish Aid</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lebanon, Palestine</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Economic Growth, Humanitarian aid, Capacity building and training, Community Development, Financial Management Services</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>09 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/announcement-of-the-polish-development-aid-2026/</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.gov.pl/web/dyplomacja/ogloszenie-konkursu-polska-pomoc-rozwojowa-2026</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Zal_do_umowy_-_Wytyczne_dotyczace_informowania_o_projektach.pdf</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MSME Consultant–Economic Empowerment for Caregivers of children engaged in worst forms of child labour–PROSPECTS Project</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Plan International</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Child Rights, Entrepreneurship, Food Security, Capacity building and training</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>30 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/msme-consultant-economic-empowerment-for-caregivers-of-children-engaged-in-worst-forms-of-child-labour-prospects-project/</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/terms_of_reference_-_prospects_msme_consultant-final.pdf, https://darpe.me/wp-content/uploads/2026/03/MSME-Consultant-.docx</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Value Chain Assessment and Prioritizing of ICT and AI Zahle</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>UNDP</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Economic Growth, Information Communication and Technology, Research and assessment</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>01 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/value-chain-assessment-and-prioritizing-of-ict-and-ai-zahle/</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43380</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNDP-LBN-01371_English.pdf, https://darpe.me/wp-content/uploads/2026/03/170570873_RFP-58-26-ICT-VALUE-CHAIN-ASSESMENT.pdf</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Provision of Services for a Biodiversity assessment within the Oustwane watershed (Akkar-Lebanon)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UNDP</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Environment and Energy, Environmental Services</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>20 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/provision-of-services-for-a-biodiversity-assessment-within-the-oustwane-watershed-akkar-lebanon/</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43201</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/169857625_RFP-50-26-Final-.pdf, https://darpe.me/wp-content/uploads/2026/03/UNDP-LBN-01357_1_SUPPLIER.pdf</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Phase-Out Assessment of the Strategic Partnership Agreement II (SPA II)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ActionAid</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Democratic Governance, Refugees and Migration, Youth Empowerment, Monitoring and evaluation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>31 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/phase-out-assessment-of-the-strategic-partnership-agreement-ii-spa-ii/</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Technical-Proposal-Template-Phase-out-Assessment-Cosultancy-1.docx, https://darpe.me/wp-content/uploads/2026/03/Financial-Proposal-Template-SPAII-Jordan-Phase-out-Assessment-1.xlsx</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Call for Applications for Grants to Support the Growth and Competitiveness of Creative Businesses</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Global Communities</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Palestine</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Economic Growth, Entrepreneurship, Capacity building and training</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>05 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://darpe.me/darpe-entries/call-for-applications-for-grants-to-support-the-growth-and-competitiveness-of-creative-businesses/</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSeI6DgkOVxMkFZ4-HyQLNmDKt24Fx5vFF5K_0gPQMgCfLWTvA/viewform</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://darpe.me/wp-content/uploads/2026/03/ar-call-for-applications-1773664090.pdf, https://darpe.me/wp-content/uploads/2026/03/eng-call-for-applications-1773664090.pdf</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tenders_grants.xlsx
+++ b/tenders_grants.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="69" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Strengthening civil society &amp; youth for climate action in Egypt – Baseline study</t>
+          <t>Recrutement d’un consultant, un cabinet ou organisme de formation spécialisé dans la comptabilité des banques chargé de renforcer les capacités des vérificateurs et cadres de la DGI (H/F)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -512,37 +512,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CARE Egypt Foundation</t>
+          <t>Expertise France</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Climate Change and Global Warming, Democratic Governance, Youth Empowerment, Monitoring and evaluation</t>
+          <t>Economic Growth, Capacity building and training</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>18 Apr 2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/strengthening-civil-society-youth-for-climate-action-in-egypt-baseline-study/</t>
+          <t>https://darpe.me/darpe-entries/recrutement-dun-consultant-un-cabinet-ou-organisme-de-formation-specialise-dans-la-comptabilite-des-banques-charge-de-renforcer-les-capacites-des-verificateurs-et-cadres-de-la-dgi-h-f/</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://care.org.eg/job/%d8%aa%d9%86%d9%81%d9%8a%d8%b0-%d8%af%d8%b1%d8%a7%d8%b3%d8%a9-%d8%ae%d8%b7-%d8%a7%d9%84%d8%a3%d8%b3%d8%a7%d8%b3/</t>
+          <t>https://expertise-france.gestmax.fr/15067/1/formation-controleurs-banques-h-f/fr_FR?backlink=search</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/BMZ-Basline-Study-TOR-en.docx, https://darpe.me/wp-content/uploads/2026/03/CEF-consultancy-TOR-in-Arabic-4.doc</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Experise-france-ll.pdf</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hiring A Social Media Agency</t>
+          <t>Recrutement d’un consultant, un cabinet ou organisme de formation spécialisé dans la comptabilité et fiscalité du secteur des télécoms chargé de renforcer les capacités des vérificateurs et cadres de la DGI (H/F)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -561,37 +561,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sawiris Foundation</t>
+          <t>Expertise France</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Economic Growth, Entrepreneurship, Women Rights and Empowerment, Youth Empowerment, Media and communication</t>
+          <t>Economic Growth, Information Communication and Technology, Capacity building and training</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>18 Apr 2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/hiring-a-social-media-agency/</t>
+          <t>https://darpe.me/darpe-entries/recrutement-dun-consultant-un-cabinet-ou-organisme-de-formation-specialise-dans-la-comptabilite-et-fiscalite-du-secteur-des-telecoms-charge-de-renforcer-les-capacites-des-verificateurs-et-ca/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://sawirisfoundation.org/consultancies/hiring-a-social-media-agency/</t>
+          <t>https://expertise-france.gestmax.fr/15068/1/formation-controleurs-telecoms-h-f/fr_FR?backlink=search</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Sawiris-Foundation_Hiring-Social-Media-Agency-1.docx</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Experise-france.pdf</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -600,7 +600,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Project to Strengthen Analytical Capabilities for System Stabilization in Lebanon</t>
+          <t>Consultancy Terms of Reference – Platform for Unified Identity and Access Management</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JICA</t>
+          <t>Al Majmoua</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -620,27 +620,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Environment and Energy, Capacity building and training, Institutional Strengthening, Research and assessment</t>
+          <t>Economic Growth, Entrepreneurship, ICT Solutions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/project-to-strengthen-analytical-capabilities-for-system-stabilization-in-lebanon/</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://www2.jica.go.jp/ja/announce/index.php?contract=1&amp;p=1&amp;fbclid=IwAR3-vltmyrwUkBXZ0hZDpVRYlCgfwWyheVk55pUsJGnkE-MVJc77vFkG2TI</t>
-        </is>
-      </c>
+          <t>https://darpe.me/darpe-entries/consultancy-terms-of-reference-platform-for-unified-identity-and-access-management/</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/20260318_255908_1_02.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/2026_rdpp_daem_idendity_and_access_management_tor.pdf</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -649,7 +645,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Guide orientation, canevas suivi-évaluation, formation Centres de jours pour personnes âgées</t>
+          <t>Audit firm recruitment to conduct audit missions for Swisscontact Lebanon Project</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,37 +655,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UN Women</t>
+          <t>Swisscontact</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Social Development, Women Rights and Empowerment, Capacity building and training, Institutional Strengthening</t>
+          <t>Economic Growth, Entrepreneurship, Accounting &amp; Auditing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>04 Apr 2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/guide-orientation-canevas-suivi-evaluation-formation-centres-de-jours-pour-personnes-agees/</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://www.ungm.org/Public/Notice/292732</t>
-        </is>
-      </c>
+          <t>https://darpe.me/darpe-entries/audit-firm-recruitment-to-conduct-audit-missions-for-swisscontact-lebanon-project/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/170424091_RFP-Centres-de-jours-PA-VF-03.03.26.docx, https://darpe.me/wp-content/uploads/2026/03/UNW-MAR-2025-00111_SUPPLIER.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/swisscontact_lebanon_audit_tor.pdf</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -698,47 +690,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Apply for ClimateLaunchpad 2026</t>
+          <t>Emergency agricultural support to conflict-affected agriculture-based families in the Gaza Strip to reactivate local food production and restore agriculture-based livelihoods</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ClimateLaunchpad</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Egypt, Morocco, Turkey</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Climate Change and Global Warming, Entrepreneurship, Capacity building and training, Environmental Services</t>
+          <t>Agriculture, Food Security, Capacity building and training, Monitoring and evaluation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/apply-for-climatelaunchpad-2026/</t>
+          <t>https://darpe.me/darpe-entries/emergency-agricultural-support-to-conflict-affected-agriculture-based-families-in-the-gaza-strip-to-reactivate-local-food-production-and-restore-agriculture-based-livelihoods/</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://climatelaunchpad.org/</t>
+          <t>https://www.ungm.org/Public/Notice/294307</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://climatelaunchpad.org/application-form/</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/IfP-FAOPAL-by-AT-18.3.2026-clean.pdf</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -747,43 +739,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The 2026-2027 ECD in Crisis Research Fellowship Program</t>
+          <t>Renforcement des capacités des membres des inspections et des cadres intermédiaires des FSI, ainsi que des directions impliquées dans l’axe redevabilité, en matière de communication professionnelle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Moving Minds Alliance</t>
+          <t>UNDP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MENA region</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Child Rights, Research and assessment</t>
+          <t>Democratic Governance, Capacity building and training</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/the-2026-2027-ecd-in-crisis-research-fellowship-program/</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>https://darpe.me/darpe-entries/renforcement-des-capacites-des-membres-des-inspections-et-des-cadres-intermediaires-des-fsi-ainsi-que-des-directions-impliquees-dans-laxe-redevabilite-en-matiere-de-communication-profession/</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43801</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/2026-27-ECDiC-Research-Fellowship-Programme-Fellows-TOR.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/172435347_TdRs-Cabinet-de-formation-PNL_1.pdf, https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNDP-TUN-009581_French.pdf</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -792,7 +788,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Establishment of Coaching &amp; Technical Experts Pool</t>
+          <t>Framework Agreement for Legal Counsel Services in Jordan and West Bank</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -802,33 +798,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Syrian Association for Relief and Development (SARD)</t>
+          <t>International development Law Organization (IDLO)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Syria, Turkey</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agriculture, Economic Growth, Entrepreneurship, Women Rights and Empowerment, Capacity building and training, Feasibility studies, Financial Management Services, Human Resources Management , Legal Services</t>
+          <t>Democratic Governance, Legal Services</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/establishment-of-coaching-technical-experts-pool/</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>https://darpe.me/darpe-entries/framework-agreement-for-legal-counsel-services-in-jordan-and-west-bank/</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.ungm.org/Public/Notice/294436</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/CALL-FOR-EXPRESSIONS-OF-INTEREST-EOI.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Retender-ITB-No.-N_231-2026_JOR_ITB-Legal-Counsel-Services.pdf</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enhancing Economic Opportunities for Women and Youth within the framework of PROJECT PIHOS–Phase 2</t>
+          <t>Consultancy Services – Development and Curation of Psychosocial Accompaniment Training Materials</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -847,37 +847,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EBRD</t>
+          <t>Anar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Entrepreneurship, Food Security, Refugees and Migration, Capacity building and training</t>
+          <t>Child Rights, Health, Capacity building and training, Psychosocial Support</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/enhancing-economic-opportunities-for-women-and-youth-within-the-framework-of-project-pihos-phase-2/</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://eu.smart.gep.com/publicrfx/ebrd?oloc=215#/</t>
-        </is>
-      </c>
+          <t>https://darpe.me/darpe-entries/consultancy-services-development-and-curation-of-psychosocial-accompaniment-training-materials/</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Event-Summary-Overview-.docx, https://darpe.me/wp-content/uploads/2026/03/French-ToRs-Gender-and-Economic-Inclusion-Technical-Assistance-Framework-FRENCH.docx, https://darpe.me/wp-content/uploads/2026/03/Access-to-Skills-ToR-Phase-2_Gender-and-Economic-Inclusion-Technical-Assistance-Framework-ENGLISH.docx</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/terms-of-reference-for-consultancy-services-final-version-1773928271.pdf</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -886,7 +882,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Recruitment of Consultancy Firm UN Women Tunisia</t>
+          <t>Preparation of an analytical research paper on the reality of water purification plants in Palestine: “Performance evaluation, governance gaps, and opportunities to maximize the use of treated water”</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -896,37 +892,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UN Women</t>
+          <t>MA`AN Development Center</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Democratic Governance, Women Rights and Empowerment, Capacity building and training</t>
+          <t>Water and Wastewater, Research and assessment</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/recruitment-of-consultancy-firm-un-women-tunisia/</t>
+          <t>https://darpe.me/darpe-entries/preparation-of-an-analytical-research-paper-on-the-reality-of-water-purification-plants-in-palestine-performance-evaluation-governance-gaps-and-opportunities-to-maximize-the-use-of-treated/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/294185</t>
+          <t>https://forms.office.com/r/aGvgmy0HVS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/172079988_Request-for-Quotation-RFQ-PBF-Expert-Consultancy-Company-Training-April-2026_VF2.docx, https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNW-TUN-2026-00009_English.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/MAAN-CENTER.pdf</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -935,7 +931,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>État des lieux et Plan d’action national pour la protection des pollinisateurs en Tunisie</t>
+          <t>La conception, le développement et le déploiement d’un Système d’Information de l’Agriculture Biologique en Tunisie (SIABT), ainsi que l’assistance à sa mise en place</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -945,7 +941,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -955,27 +951,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Agriculture, Environment and Energy, Institutional Strengthening, Research and assessment</t>
+          <t>Agriculture, Climate Change and Global Warming, ICT Solutions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/etat-des-lieux-et-plan-daction-national-pour-la-protection-des-pollinisateurs-en-tunisie/</t>
+          <t>https://darpe.me/darpe-entries/la-conception-le-developpement-et-le-deploiement-dun-systeme-dinformation-de-lagriculture-biologique-en-tunisie-siabt-ainsi-que-lassistance-a-sa-mise-en-place/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43302</t>
+          <t>https://www.ungm.org/Public/Notice/294411</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/170284814_TERMES-DE-REFERENCE_pollinisateurs_-VFF.docx, https://darpe.me/wp-content/uploads/2026/03/UNDP-TUN-00950_SUPPLIER.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/RFP032026_SIABT-BIOREST.pdf</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -984,7 +980,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Digitalisation du Manuel de l’Offre de Services de Placement à l’International de l’ANAPEC.</t>
+          <t>Call for Proposals (ToR) – Rapid Needs and Vulnerability Assessment and Targeting Package for Cash-for-Work (CfW)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -994,37 +990,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>MA`AN Development Center</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Economic Growth, Entrepreneurship, ICT Solutions</t>
+          <t>Humanitarian aid, Engineering services</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05 Apr 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/digitalisation-du-manuel-de-loffre-de-services-de-placement-a-linternational-de-lanapec/</t>
+          <t>https://darpe.me/darpe-entries/call-for-proposals-tor-rapid-needs-and-vulnerability-assessment-and-targeting-package-for-cash-for-work-cfw/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/294207</t>
+          <t>https://forms.office.com/r/ixZVZdvATt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/RFQ_Services_FR-1.pdf, https://darpe.me/wp-content/uploads/2026/03/TDR_Digitalisation_Manuel_Offre_Services_ANAPEC_OIT-VF.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Call-for-Proposals-ToR-.pdf</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1033,7 +1029,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Provision of Digital Product Passport (DPP) Pilot Implementation Services for Textile SMEs in Egypt</t>
+          <t>MTF/INT/943/MUL baby project 35 : Services de collecte de données de pêche</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1043,37 +1039,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIDO</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Entrepreneurship, Industry, ICT Solutions</t>
+          <t>Agriculture, Research and assessment</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>05 Apr 2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/provision-of-digital-product-passport-dpp-pilot-implementation-services-for-textile-smes-in-egypt/</t>
+          <t>https://darpe.me/darpe-entries/mtf-int-943-mul-baby-project-35-services-de-collecte-de-donnees-de-peche/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.unido.org/get-involved/procurement/procurement-opportunities</t>
+          <t>https://www.ungm.org/Public/Notice/294419</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/TOR_TIGARA-DPP.pdf, https://darpe.me/wp-content/uploads/2026/03/RFx-7000008382-instructions-to-bidders.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/ITB_Goods_Marine-Data-Protection.pdf</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1082,7 +1078,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Call for expression of interest from Egyptian SMEs: Demonstration of Resource Efficient production in Automotive, Electric and Electronics sectors</t>
+          <t>RFP: JONAP II Evaluation Assessment</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1092,37 +1088,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNIDO</t>
+          <t>UN Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Entrepreneurship, Industry, Waste Management, Business Development, Capacity building and training</t>
+          <t>Democratic Governance, Women Rights and Empowerment, Monitoring and evaluation</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/call-for-expression-of-interest-from-egyptian-smes-demonstration-of-resource-efficient-production-in-automotive-electric-and-electronics-sectors-in-arabic/</t>
+          <t>https://darpe.me/darpe-entries/rfp-jonap-ii-evaluation-assessment/</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://greenforwardindustry.eu/news/eoi-demonstration-resource-efficient-production-egypt-automotive-sector/</t>
+          <t>https://www.ungm.org/Public/Notice/294425</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://forms.office.com/Pages/ResponsePage.aspx?id=MUlqQlzsy0-dEDNj69-SgAAXvVZaHG1DrWaMyOV_m8FUQkFRV0U2VkdCRVQ2M1RYOFE4TEhPU05LTS4u</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNW-JOR-2026-00006_English.pdf, https://darpe.me/wp-content/uploads/2026/03/172389276_RFP-WPS-Programme-Evaluation.docx</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1131,7 +1127,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Call for Consultants-Generic call for trainers</t>
+          <t>Bureau d’étude pour l’accompagnement du système de contrôle officiel en Agriculture Biologique de la Direction Générale de l’Agriculture Biologique (DGAB)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1141,37 +1137,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ABAAD</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Democratic Governance, Capacity building and training</t>
+          <t>Agriculture, Climate Change and Global Warming, Accounting &amp; Auditing, Institutional Strengthening</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/call-for-consultants-generic-call-for-trainers/</t>
+          <t>https://darpe.me/darpe-entries/bureau-detude-pour-laccompagnement-du-systeme-de-controle-officiel-en-agriculture-biologique-de-la-direction-generale-de-lagriculture-biologique-dgab/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://ee-eu.kobotoolbox.org/x/ny5U9FMs</t>
+          <t>https://www.ungm.org/Public/Notice/294432</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Generic-call-for-trainers.docx</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/RFP022026-ISO-17020-BIORESTV.pdf</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1180,7 +1176,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Recrutement Formateur/trice en Entrepreneuriat</t>
+          <t>Finalisation des annexes de la proposition financière du projet GCF Barrage vert</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1190,33 +1186,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Création et Créativité pour le Développement et l`embauche (CCDE)</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Economic Growth, Capacity building and training</t>
+          <t>Climate Change and Global Warming, Environment and Energy, Business Development</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/recrutement-formateur-trice-en-entrepreneuriat/</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>https://darpe.me/darpe-entries/finalisation-des-annexes-de-la-proposition-financiere-du-projet-gcf-barrage-vert/</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.ungm.org/Public/Notice/294448</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Recrutement-Formateur-trice-en-Entrepreneuriat.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/2026FNALGFNALG136153-I-Finalisation-des-annexes-GCF-Signe.pdf</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1225,47 +1225,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Call for Proposals of the Facility Investing for Employment (IFE)</t>
+          <t>Strengthening civil society &amp; youth for climate action in Egypt – Baseline study</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Invest for Jobs</t>
+          <t>CARE Egypt Foundation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Egypt, Morocco, Tunisia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Economic Growth, Capacity building and training</t>
+          <t>Climate Change and Global Warming, Democratic Governance, Youth Empowerment, Monitoring and evaluation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>01 Jun 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/call-for-proposals-of-the-facility-investing-for-employment-ife/</t>
+          <t>https://darpe.me/darpe-entries/strengthening-civil-society-youth-for-climate-action-in-egypt-baseline-study/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://invest-for-jobs.com/en/ife-download-center</t>
+          <t>https://care.org.eg/job/%d8%aa%d9%86%d9%81%d9%8a%d8%b0-%d8%af%d8%b1%d8%a7%d8%b3%d8%a9-%d8%ae%d8%b7-%d8%a7%d9%84%d8%a3%d8%b3%d8%a7%d8%b3/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Guidelines-for-Applicants-CfP-2026-Labour-Migration-final-05-03-2026.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/BMZ-Basline-Study-TOR-en.docx, https://darpe.me/wp-content/uploads/2026/03/CEF-consultancy-TOR-in-Arabic-4.doc</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1274,47 +1274,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Announcement of the “Polish Development Aid 2026”</t>
+          <t>Hiring A Social Media Agency</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Polish Aid</t>
+          <t>Sawiris Foundation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lebanon, Palestine</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Economic Growth, Humanitarian aid, Capacity building and training, Community Development, Financial Management Services</t>
+          <t>Economic Growth, Entrepreneurship, Women Rights and Empowerment, Youth Empowerment, Media and communication</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/announcement-of-the-polish-development-aid-2026/</t>
+          <t>https://darpe.me/darpe-entries/hiring-a-social-media-agency/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.gov.pl/web/dyplomacja/ogloszenie-konkursu-polska-pomoc-rozwojowa-2026</t>
+          <t>https://sawirisfoundation.org/consultancies/hiring-a-social-media-agency/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Zal_do_umowy_-_Wytyczne_dotyczace_informowania_o_projektach.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Sawiris-Foundation_Hiring-Social-Media-Agency-1.docx</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSME Consultant–Economic Empowerment for Caregivers of children engaged in worst forms of child labour–PROSPECTS Project</t>
+          <t>Project to Strengthen Analytical Capabilities for System Stabilization in Lebanon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plan International</t>
+          <t>JICA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1343,23 +1343,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Child Rights, Entrepreneurship, Food Security, Capacity building and training</t>
+          <t>Environment and Energy, Capacity building and training, Institutional Strengthening, Research and assessment</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/msme-consultant-economic-empowerment-for-caregivers-of-children-engaged-in-worst-forms-of-child-labour-prospects-project/</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>https://darpe.me/darpe-entries/project-to-strengthen-analytical-capabilities-for-system-stabilization-in-lebanon/</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www2.jica.go.jp/ja/announce/index.php?contract=1&amp;p=1&amp;fbclid=IwAR3-vltmyrwUkBXZ0hZDpVRYlCgfwWyheVk55pUsJGnkE-MVJc77vFkG2TI</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/terms_of_reference_-_prospects_msme_consultant-final.pdf, https://darpe.me/wp-content/uploads/2026/03/MSME-Consultant-.docx</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/20260318_255908_1_02.pdf</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1368,7 +1372,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Value Chain Assessment and Prioritizing of ICT and AI Zahle</t>
+          <t>Guide orientation, canevas suivi-évaluation, formation Centres de jours pour personnes âgées</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1378,37 +1382,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>UN Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Economic Growth, Information Communication and Technology, Research and assessment</t>
+          <t>Social Development, Women Rights and Empowerment, Capacity building and training, Institutional Strengthening</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/value-chain-assessment-and-prioritizing-of-ict-and-ai-zahle/</t>
+          <t>https://darpe.me/darpe-entries/guide-orientation-canevas-suivi-evaluation-formation-centres-de-jours-pour-personnes-agees/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43380</t>
+          <t>https://www.ungm.org/Public/Notice/292732</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNDP-LBN-01371_English.pdf, https://darpe.me/wp-content/uploads/2026/03/170570873_RFP-58-26-ICT-VALUE-CHAIN-ASSESMENT.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/170424091_RFP-Centres-de-jours-PA-VF-03.03.26.docx, https://darpe.me/wp-content/uploads/2026/03/UNW-MAR-2025-00111_SUPPLIER.pdf</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1417,7 +1421,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Provision of Services for a Biodiversity assessment within the Oustwane watershed (Akkar-Lebanon)</t>
+          <t>Apply for ClimateLaunchpad 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1427,37 +1431,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>ClimateLaunchpad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Egypt, Morocco, Turkey</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Environment and Energy, Environmental Services</t>
+          <t>Climate Change and Global Warming, Entrepreneurship, Capacity building and training, Environmental Services</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/provision-of-services-for-a-biodiversity-assessment-within-the-oustwane-watershed-akkar-lebanon/</t>
+          <t>https://darpe.me/darpe-entries/apply-for-climatelaunchpad-2026/</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43201</t>
+          <t>https://climatelaunchpad.org/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/169857625_RFP-50-26-Final-.pdf, https://darpe.me/wp-content/uploads/2026/03/UNDP-LBN-01357_1_SUPPLIER.pdf</t>
+          <t>https://climatelaunchpad.org/application-form/</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1466,27 +1470,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Phase-Out Assessment of the Strategic Partnership Agreement II (SPA II)</t>
+          <t>The 2026-2027 ECD in Crisis Research Fellowship Program</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ActionAid</t>
+          <t>Moving Minds Alliance</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>MENA region</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Democratic Governance, Refugees and Migration, Youth Empowerment, Monitoring and evaluation</t>
+          <t>Child Rights, Research and assessment</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1496,13 +1500,13 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/phase-out-assessment-of-the-strategic-partnership-agreement-ii-spa-ii/</t>
+          <t>https://darpe.me/darpe-entries/the-2026-2027-ecd-in-crisis-research-fellowship-program/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Technical-Proposal-Template-Phase-out-Assessment-Cosultancy-1.docx, https://darpe.me/wp-content/uploads/2026/03/Financial-Proposal-Template-SPAII-Jordan-Phase-out-Assessment-1.xlsx</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/2026-27-ECDiC-Research-Fellowship-Programme-Fellows-TOR.pdf</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1511,47 +1515,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Call for Applications for Grants to Support the Growth and Competitiveness of Creative Businesses</t>
+          <t>Establishment of Coaching &amp; Technical Experts Pool</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Global Communities</t>
+          <t>Syrian Association for Relief and Development (SARD)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Palestine</t>
+          <t>Syria, Turkey</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Economic Growth, Entrepreneurship, Capacity building and training</t>
+          <t>Agriculture, Economic Growth, Entrepreneurship, Women Rights and Empowerment, Capacity building and training, Feasibility studies, Financial Management Services, Human Resources Management , Legal Services</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>05 Apr 2026</t>
+          <t>29 Mar 2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/call-for-applications-for-grants-to-support-the-growth-and-competitiveness-of-creative-businesses/</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://docs.google.com/forms/d/e/1FAIpQLSeI6DgkOVxMkFZ4-HyQLNmDKt24Fx5vFF5K_0gPQMgCfLWTvA/viewform</t>
-        </is>
-      </c>
+          <t>https://darpe.me/darpe-entries/establishment-of-coaching-technical-experts-pool/</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/ar-call-for-applications-1773664090.pdf, https://darpe.me/wp-content/uploads/2026/03/eng-call-for-applications-1773664090.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/CALL-FOR-EXPRESSIONS-OF-INTEREST-EOI.pdf</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>

--- a/tenders_grants.xlsx
+++ b/tenders_grants.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
@@ -502,47 +502,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Recrutement d’un consultant, un cabinet ou organisme de formation spécialisé dans la comptabilité des banques chargé de renforcer les capacités des vérificateurs et cadres de la DGI (H/F)</t>
+          <t>Call for Nominations: Annual Award for Development (Extended)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Expertise France</t>
+          <t>OPEC Fund for International Development (OFID)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Algeria, Iraq, Kuwait, Libya, Saudi Arabia, United Arab Emirates</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Economic Growth, Capacity building and training</t>
+          <t>Climate Change and Global Warming, Entrepreneurship, Environment and Energy, Food Security, Information Communication and Technology, Urban &amp; Rural Development, Community Development, Development Finance</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18 Apr 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/recrutement-dun-consultant-un-cabinet-ou-organisme-de-formation-specialise-dans-la-comptabilite-des-banques-charge-de-renforcer-les-capacites-des-verificateurs-et-cadres-de-la-dgi-h-f/</t>
+          <t>https://darpe.me/darpe-entries/call-for-nominations-annual-award-for-development/</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://expertise-france.gestmax.fr/15067/1/formation-controleurs-banques-h-f/fr_FR?backlink=search</t>
+          <t>https://opecfund.org/what-we-do/special-initiatives/annual-award</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Experise-france-ll.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/2026-AAW-Flyer-ThreeCategories-FINAL.pdf</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Recrutement d’un consultant, un cabinet ou organisme de formation spécialisé dans la comptabilité et fiscalité du secteur des télécoms chargé de renforcer les capacités des vérificateurs et cadres de la DGI (H/F)</t>
+          <t>Recrutement d’un consultant, un cabinet ou organisme de formation spécialisé dans la comptabilité des banques chargé de renforcer les capacités des vérificateurs et cadres de la DGI (H/F)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Economic Growth, Information Communication and Technology, Capacity building and training</t>
+          <t>Economic Growth, Capacity building and training</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -581,17 +581,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/recrutement-dun-consultant-un-cabinet-ou-organisme-de-formation-specialise-dans-la-comptabilite-et-fiscalite-du-secteur-des-telecoms-charge-de-renforcer-les-capacites-des-verificateurs-et-ca/</t>
+          <t>https://darpe.me/darpe-entries/recrutement-dun-consultant-un-cabinet-ou-organisme-de-formation-specialise-dans-la-comptabilite-des-banques-charge-de-renforcer-les-capacites-des-verificateurs-et-cadres-de-la-dgi-h-f/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://expertise-france.gestmax.fr/15068/1/formation-controleurs-telecoms-h-f/fr_FR?backlink=search</t>
+          <t>https://expertise-france.gestmax.fr/15067/1/formation-controleurs-banques-h-f/fr_FR?backlink=search</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Experise-france.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Experise-france-ll.pdf</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -600,7 +600,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consultancy Terms of Reference – Platform for Unified Identity and Access Management</t>
+          <t>Recrutement d’un consultant, un cabinet ou organisme de formation spécialisé dans la comptabilité et fiscalité du secteur des télécoms chargé de renforcer les capacités des vérificateurs et cadres de la DGI (H/F)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -610,33 +610,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Al Majmoua</t>
+          <t>Expertise France</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Economic Growth, Entrepreneurship, ICT Solutions</t>
+          <t>Economic Growth, Information Communication and Technology, Capacity building and training</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>18 Apr 2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/consultancy-terms-of-reference-platform-for-unified-identity-and-access-management/</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>https://darpe.me/darpe-entries/recrutement-dun-consultant-un-cabinet-ou-organisme-de-formation-specialise-dans-la-comptabilite-et-fiscalite-du-secteur-des-telecoms-charge-de-renforcer-les-capacites-des-verificateurs-et-ca/</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://expertise-france.gestmax.fr/15068/1/formation-controleurs-telecoms-h-f/fr_FR?backlink=search</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/2026_rdpp_daem_idendity_and_access_management_tor.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Experise-france.pdf</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -645,7 +649,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Audit firm recruitment to conduct audit missions for Swisscontact Lebanon Project</t>
+          <t>Consultancy Terms of Reference – Platform for Unified Identity and Access Management</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,7 +659,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Swisscontact</t>
+          <t>Al Majmoua</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -665,23 +669,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Economic Growth, Entrepreneurship, Accounting &amp; Auditing</t>
+          <t>Economic Growth, Entrepreneurship, ICT Solutions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>04 Apr 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/audit-firm-recruitment-to-conduct-audit-missions-for-swisscontact-lebanon-project/</t>
+          <t>https://darpe.me/darpe-entries/consultancy-terms-of-reference-platform-for-unified-identity-and-access-management/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/swisscontact_lebanon_audit_tor.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/2026_rdpp_daem_idendity_and_access_management_tor.pdf</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -690,47 +694,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Emergency agricultural support to conflict-affected agriculture-based families in the Gaza Strip to reactivate local food production and restore agriculture-based livelihoods</t>
+          <t>Audit firm recruitment to conduct audit missions for Swisscontact Lebanon Project</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FAO</t>
+          <t>Swisscontact</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Palestine</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agriculture, Food Security, Capacity building and training, Monitoring and evaluation</t>
+          <t>Economic Growth, Entrepreneurship, Accounting &amp; Auditing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>04 Apr 2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/emergency-agricultural-support-to-conflict-affected-agriculture-based-families-in-the-gaza-strip-to-reactivate-local-food-production-and-restore-agriculture-based-livelihoods/</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://www.ungm.org/Public/Notice/294307</t>
-        </is>
-      </c>
+          <t>https://darpe.me/darpe-entries/audit-firm-recruitment-to-conduct-audit-missions-for-swisscontact-lebanon-project/</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/IfP-FAOPAL-by-AT-18.3.2026-clean.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/swisscontact_lebanon_audit_tor.pdf</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -739,47 +739,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Renforcement des capacités des membres des inspections et des cadres intermédiaires des FSI, ainsi que des directions impliquées dans l’axe redevabilité, en matière de communication professionnelle</t>
+          <t>Emergency agricultural support to conflict-affected agriculture-based families in the Gaza Strip to reactivate local food production and restore agriculture-based livelihoods</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Democratic Governance, Capacity building and training</t>
+          <t>Agriculture, Food Security, Capacity building and training, Monitoring and evaluation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/renforcement-des-capacites-des-membres-des-inspections-et-des-cadres-intermediaires-des-fsi-ainsi-que-des-directions-impliquees-dans-laxe-redevabilite-en-matiere-de-communication-profession/</t>
+          <t>https://darpe.me/darpe-entries/emergency-agricultural-support-to-conflict-affected-agriculture-based-families-in-the-gaza-strip-to-reactivate-local-food-production-and-restore-agriculture-based-livelihoods/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43801</t>
+          <t>https://www.ungm.org/Public/Notice/294307</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/172435347_TdRs-Cabinet-de-formation-PNL_1.pdf, https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNDP-TUN-009581_French.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/IfP-FAOPAL-by-AT-18.3.2026-clean.pdf</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -788,7 +788,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Framework Agreement for Legal Counsel Services in Jordan and West Bank</t>
+          <t>Renforcement des capacités des membres des inspections et des cadres intermédiaires des FSI, ainsi que des directions impliquées dans l’axe redevabilité, en matière de communication professionnelle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>International development Law Organization (IDLO)</t>
+          <t>UNDP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Palestine</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Democratic Governance, Legal Services</t>
+          <t>Democratic Governance, Capacity building and training</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/framework-agreement-for-legal-counsel-services-in-jordan-and-west-bank/</t>
+          <t>https://darpe.me/darpe-entries/renforcement-des-capacites-des-membres-des-inspections-et-des-cadres-intermediaires-des-fsi-ainsi-que-des-directions-impliquees-dans-laxe-redevabilite-en-matiere-de-communication-profession/</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/294436</t>
+          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43801</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Retender-ITB-No.-N_231-2026_JOR_ITB-Legal-Counsel-Services.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/172435347_TdRs-Cabinet-de-formation-PNL_1.pdf, https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNDP-TUN-009581_French.pdf</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consultancy Services – Development and Curation of Psychosocial Accompaniment Training Materials</t>
+          <t>Framework Agreement for Legal Counsel Services in Jordan and West Bank</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anar</t>
+          <t>International development Law Organization (IDLO)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Child Rights, Health, Capacity building and training, Psychosocial Support</t>
+          <t>Democratic Governance, Legal Services</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -867,13 +867,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/consultancy-services-development-and-curation-of-psychosocial-accompaniment-training-materials/</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>https://darpe.me/darpe-entries/framework-agreement-for-legal-counsel-services-in-jordan-and-west-bank/</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.ungm.org/Public/Notice/294436</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/terms-of-reference-for-consultancy-services-final-version-1773928271.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Retender-ITB-No.-N_231-2026_JOR_ITB-Legal-Counsel-Services.pdf</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -882,7 +886,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Preparation of an analytical research paper on the reality of water purification plants in Palestine: “Performance evaluation, governance gaps, and opportunities to maximize the use of treated water”</t>
+          <t>Consultancy Services – Development and Curation of Psychosocial Accompaniment Training Materials</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -892,7 +896,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MA`AN Development Center</t>
+          <t>Anar</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -902,27 +906,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Water and Wastewater, Research and assessment</t>
+          <t>Child Rights, Health, Capacity building and training, Psychosocial Support</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/preparation-of-an-analytical-research-paper-on-the-reality-of-water-purification-plants-in-palestine-performance-evaluation-governance-gaps-and-opportunities-to-maximize-the-use-of-treated/</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://forms.office.com/r/aGvgmy0HVS</t>
-        </is>
-      </c>
+          <t>https://darpe.me/darpe-entries/consultancy-services-development-and-curation-of-psychosocial-accompaniment-training-materials/</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/MAAN-CENTER.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/terms-of-reference-for-consultancy-services-final-version-1773928271.pdf</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -931,7 +931,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>La conception, le développement et le déploiement d’un Système d’Information de l’Agriculture Biologique en Tunisie (SIABT), ainsi que l’assistance à sa mise en place</t>
+          <t>Preparation of an analytical research paper on the reality of water purification plants in Palestine: “Performance evaluation, governance gaps, and opportunities to maximize the use of treated water”</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -941,37 +941,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FAO</t>
+          <t>MA`AN Development Center</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Agriculture, Climate Change and Global Warming, ICT Solutions</t>
+          <t>Water and Wastewater, Research and assessment</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/la-conception-le-developpement-et-le-deploiement-dun-systeme-dinformation-de-lagriculture-biologique-en-tunisie-siabt-ainsi-que-lassistance-a-sa-mise-en-place/</t>
+          <t>https://darpe.me/darpe-entries/preparation-of-an-analytical-research-paper-on-the-reality-of-water-purification-plants-in-palestine-performance-evaluation-governance-gaps-and-opportunities-to-maximize-the-use-of-treated/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/294411</t>
+          <t>https://forms.office.com/r/aGvgmy0HVS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/RFP032026_SIABT-BIOREST.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/MAAN-CENTER.pdf</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -980,7 +980,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Call for Proposals (ToR) – Rapid Needs and Vulnerability Assessment and Targeting Package for Cash-for-Work (CfW)</t>
+          <t>La conception, le développement et le déploiement d’un Système d’Information de l’Agriculture Biologique en Tunisie (SIABT), ainsi que l’assistance à sa mise en place</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -990,37 +990,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MA`AN Development Center</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Palestine</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Humanitarian aid, Engineering services</t>
+          <t>Agriculture, Climate Change and Global Warming, ICT Solutions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/call-for-proposals-tor-rapid-needs-and-vulnerability-assessment-and-targeting-package-for-cash-for-work-cfw/</t>
+          <t>https://darpe.me/darpe-entries/la-conception-le-developpement-et-le-deploiement-dun-systeme-dinformation-de-lagriculture-biologique-en-tunisie-siabt-ainsi-que-lassistance-a-sa-mise-en-place/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://forms.office.com/r/ixZVZdvATt</t>
+          <t>https://www.ungm.org/Public/Notice/294411</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Call-for-Proposals-ToR-.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/RFP032026_SIABT-BIOREST.pdf</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MTF/INT/943/MUL baby project 35 : Services de collecte de données de pêche</t>
+          <t>Call for Proposals (ToR) – Rapid Needs and Vulnerability Assessment and Targeting Package for Cash-for-Work (CfW)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1039,37 +1039,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FAO</t>
+          <t>MA`AN Development Center</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Agriculture, Research and assessment</t>
+          <t>Humanitarian aid, Engineering services</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05 Apr 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/mtf-int-943-mul-baby-project-35-services-de-collecte-de-donnees-de-peche/</t>
+          <t>https://darpe.me/darpe-entries/call-for-proposals-tor-rapid-needs-and-vulnerability-assessment-and-targeting-package-for-cash-for-work-cfw/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/294419</t>
+          <t>https://forms.office.com/r/ixZVZdvATt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/ITB_Goods_Marine-Data-Protection.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Call-for-Proposals-ToR-.pdf</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RFP: JONAP II Evaluation Assessment</t>
+          <t>MTF/INT/943/MUL baby project 35 : Services de collecte de données de pêche</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1088,37 +1088,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UN Women</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Democratic Governance, Women Rights and Empowerment, Monitoring and evaluation</t>
+          <t>Agriculture, Research and assessment</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>05 Apr 2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/rfp-jonap-ii-evaluation-assessment/</t>
+          <t>https://darpe.me/darpe-entries/mtf-int-943-mul-baby-project-35-services-de-collecte-de-donnees-de-peche/</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/294425</t>
+          <t>https://www.ungm.org/Public/Notice/294419</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNW-JOR-2026-00006_English.pdf, https://darpe.me/wp-content/uploads/2026/03/172389276_RFP-WPS-Programme-Evaluation.docx</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/ITB_Goods_Marine-Data-Protection.pdf</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bureau d’étude pour l’accompagnement du système de contrôle officiel en Agriculture Biologique de la Direction Générale de l’Agriculture Biologique (DGAB)</t>
+          <t>RFP: JONAP II Evaluation Assessment</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FAO</t>
+          <t>UN Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Agriculture, Climate Change and Global Warming, Accounting &amp; Auditing, Institutional Strengthening</t>
+          <t>Democratic Governance, Women Rights and Empowerment, Monitoring and evaluation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/bureau-detude-pour-laccompagnement-du-systeme-de-controle-officiel-en-agriculture-biologique-de-la-direction-generale-de-lagriculture-biologique-dgab/</t>
+          <t>https://darpe.me/darpe-entries/rfp-jonap-ii-evaluation-assessment/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/294432</t>
+          <t>https://www.ungm.org/Public/Notice/294425</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/RFP022026-ISO-17020-BIORESTV.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/UN_Supplier_Negotiation_UNW-JOR-2026-00006_English.pdf, https://darpe.me/wp-content/uploads/2026/03/172389276_RFP-WPS-Programme-Evaluation.docx</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1176,7 +1176,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finalisation des annexes de la proposition financière du projet GCF Barrage vert</t>
+          <t>Bureau d’étude pour l’accompagnement du système de contrôle officiel en Agriculture Biologique de la Direction Générale de l’Agriculture Biologique (DGAB)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1191,32 +1191,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Climate Change and Global Warming, Environment and Energy, Business Development</t>
+          <t>Agriculture, Climate Change and Global Warming, Accounting &amp; Auditing, Institutional Strengthening</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/finalisation-des-annexes-de-la-proposition-financiere-du-projet-gcf-barrage-vert/</t>
+          <t>https://darpe.me/darpe-entries/bureau-detude-pour-laccompagnement-du-systeme-de-controle-officiel-en-agriculture-biologique-de-la-direction-generale-de-lagriculture-biologique-dgab/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/294448</t>
+          <t>https://www.ungm.org/Public/Notice/294432</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/2026FNALGFNALG136153-I-Finalisation-des-annexes-GCF-Signe.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/RFP022026-ISO-17020-BIORESTV.pdf</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Strengthening civil society &amp; youth for climate action in Egypt – Baseline study</t>
+          <t>Finalisation des annexes de la proposition financière du projet GCF Barrage vert</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1235,37 +1235,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CARE Egypt Foundation</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Climate Change and Global Warming, Democratic Governance, Youth Empowerment, Monitoring and evaluation</t>
+          <t>Climate Change and Global Warming, Environment and Energy, Business Development</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/strengthening-civil-society-youth-for-climate-action-in-egypt-baseline-study/</t>
+          <t>https://darpe.me/darpe-entries/finalisation-des-annexes-de-la-proposition-financiere-du-projet-gcf-barrage-vert/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://care.org.eg/job/%d8%aa%d9%86%d9%81%d9%8a%d8%b0-%d8%af%d8%b1%d8%a7%d8%b3%d8%a9-%d8%ae%d8%b7-%d8%a7%d9%84%d8%a3%d8%b3%d8%a7%d8%b3/</t>
+          <t>https://www.ungm.org/Public/Notice/294448</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/BMZ-Basline-Study-TOR-en.docx, https://darpe.me/wp-content/uploads/2026/03/CEF-consultancy-TOR-in-Arabic-4.doc</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/2026FNALGFNALG136153-I-Finalisation-des-annexes-GCF-Signe.pdf</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1274,7 +1274,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hiring A Social Media Agency</t>
+          <t>Strengthening civil society &amp; youth for climate action in Egypt – Baseline study</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sawiris Foundation</t>
+          <t>CARE Egypt Foundation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1294,27 +1294,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Economic Growth, Entrepreneurship, Women Rights and Empowerment, Youth Empowerment, Media and communication</t>
+          <t>Climate Change and Global Warming, Democratic Governance, Youth Empowerment, Monitoring and evaluation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/hiring-a-social-media-agency/</t>
+          <t>https://darpe.me/darpe-entries/strengthening-civil-society-youth-for-climate-action-in-egypt-baseline-study/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://sawirisfoundation.org/consultancies/hiring-a-social-media-agency/</t>
+          <t>https://care.org.eg/job/%d8%aa%d9%86%d9%81%d9%8a%d8%b0-%d8%af%d8%b1%d8%a7%d8%b3%d8%a9-%d8%ae%d8%b7-%d8%a7%d9%84%d8%a3%d8%b3%d8%a7%d8%b3/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/Sawiris-Foundation_Hiring-Social-Media-Agency-1.docx</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/BMZ-Basline-Study-TOR-en.docx, https://darpe.me/wp-content/uploads/2026/03/CEF-consultancy-TOR-in-Arabic-4.doc</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Project to Strengthen Analytical Capabilities for System Stabilization in Lebanon</t>
+          <t>Hiring A Social Media Agency</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1333,37 +1333,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JICA</t>
+          <t>Sawiris Foundation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Environment and Energy, Capacity building and training, Institutional Strengthening, Research and assessment</t>
+          <t>Economic Growth, Entrepreneurship, Women Rights and Empowerment, Youth Empowerment, Media and communication</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/project-to-strengthen-analytical-capabilities-for-system-stabilization-in-lebanon/</t>
+          <t>https://darpe.me/darpe-entries/hiring-a-social-media-agency/</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www2.jica.go.jp/ja/announce/index.php?contract=1&amp;p=1&amp;fbclid=IwAR3-vltmyrwUkBXZ0hZDpVRYlCgfwWyheVk55pUsJGnkE-MVJc77vFkG2TI</t>
+          <t>https://sawirisfoundation.org/consultancies/hiring-a-social-media-agency/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/20260318_255908_1_02.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/Sawiris-Foundation_Hiring-Social-Media-Agency-1.docx</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Guide orientation, canevas suivi-évaluation, formation Centres de jours pour personnes âgées</t>
+          <t>Project to Strengthen Analytical Capabilities for System Stabilization in Lebanon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1382,37 +1382,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UN Women</t>
+          <t>JICA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Social Development, Women Rights and Empowerment, Capacity building and training, Institutional Strengthening</t>
+          <t>Environment and Energy, Capacity building and training, Institutional Strengthening, Research and assessment</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/guide-orientation-canevas-suivi-evaluation-formation-centres-de-jours-pour-personnes-agees/</t>
+          <t>https://darpe.me/darpe-entries/project-to-strengthen-analytical-capabilities-for-system-stabilization-in-lebanon/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.ungm.org/Public/Notice/292732</t>
+          <t>https://www2.jica.go.jp/ja/announce/index.php?contract=1&amp;p=1&amp;fbclid=IwAR3-vltmyrwUkBXZ0hZDpVRYlCgfwWyheVk55pUsJGnkE-MVJc77vFkG2TI</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/170424091_RFP-Centres-de-jours-PA-VF-03.03.26.docx, https://darpe.me/wp-content/uploads/2026/03/UNW-MAR-2025-00111_SUPPLIER.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/20260318_255908_1_02.pdf</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1421,7 +1421,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Apply for ClimateLaunchpad 2026</t>
+          <t>Guide orientation, canevas suivi-évaluation, formation Centres de jours pour personnes âgées</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ClimateLaunchpad</t>
+          <t>UN Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Egypt, Morocco, Turkey</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Climate Change and Global Warming, Entrepreneurship, Capacity building and training, Environmental Services</t>
+          <t>Social Development, Women Rights and Empowerment, Capacity building and training, Institutional Strengthening</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/apply-for-climatelaunchpad-2026/</t>
+          <t>https://darpe.me/darpe-entries/guide-orientation-canevas-suivi-evaluation-formation-centres-de-jours-pour-personnes-agees/</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://climatelaunchpad.org/</t>
+          <t>https://www.ungm.org/Public/Notice/292732</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://climatelaunchpad.org/application-form/</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/170424091_RFP-Centres-de-jours-PA-VF-03.03.26.docx, https://darpe.me/wp-content/uploads/2026/03/UNW-MAR-2025-00111_SUPPLIER.pdf</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1470,43 +1470,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>The 2026-2027 ECD in Crisis Research Fellowship Program</t>
+          <t>Apply for ClimateLaunchpad 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Moving Minds Alliance</t>
+          <t>ClimateLaunchpad</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MENA region</t>
+          <t>Egypt, Morocco, Turkey</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Child Rights, Research and assessment</t>
+          <t>Climate Change and Global Warming, Entrepreneurship, Capacity building and training, Environmental Services</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/the-2026-2027-ecd-in-crisis-research-fellowship-program/</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>https://darpe.me/darpe-entries/apply-for-climatelaunchpad-2026/</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://climatelaunchpad.org/</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/2026-27-ECDiC-Research-Fellowship-Programme-Fellows-TOR.pdf</t>
+          <t>https://climatelaunchpad.org/application-form/</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1515,43 +1519,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Establishment of Coaching &amp; Technical Experts Pool</t>
+          <t>The 2026-2027 ECD in Crisis Research Fellowship Program</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Syrian Association for Relief and Development (SARD)</t>
+          <t>Moving Minds Alliance</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Syria, Turkey</t>
+          <t>MENA region</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Agriculture, Economic Growth, Entrepreneurship, Women Rights and Empowerment, Capacity building and training, Feasibility studies, Financial Management Services, Human Resources Management , Legal Services</t>
+          <t>Child Rights, Research and assessment</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://darpe.me/darpe-entries/establishment-of-coaching-technical-experts-pool/</t>
+          <t>https://darpe.me/darpe-entries/the-2026-2027-ecd-in-crisis-research-fellowship-program/</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://darpe.me/wp-content/uploads/2026/03/CALL-FOR-EXPRESSIONS-OF-INTEREST-EOI.pdf</t>
+          <t>https://darpe.me/wp-content/uploads/2026/03/2026-27-ECDiC-Research-Fellowship-Programme-Fellows-TOR.pdf</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
